--- a/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/Otolemur garnetti.xlsx
+++ b/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/Otolemur garnetti.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachael\OneDrive\Documents\PS30094 Dissertation\Brain area data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0B10DC-CC7D-4E26-B9BA-E911AC8BADA9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BA0B10DC-CC7D-4E26-B9BA-E911AC8BADA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DADCB390-E54D-6B43-81B9-0F9FC823F6C7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0E51E8C7-A1E0-4813-991F-3B13C7191B5A}"/>
+    <workbookView xWindow="6740" yWindow="1840" windowWidth="24400" windowHeight="18440" xr2:uid="{0E51E8C7-A1E0-4813-991F-3B13C7191B5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -241,7 +252,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,9 +402,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -431,7 +442,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -537,7 +548,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -679,7 +690,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -688,9 +699,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C357EA30-AD16-4068-A61A-BC1368BF75F1}">
   <dimension ref="A1:S23"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.5">
+    <row r="1" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -734,7 +745,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.5">
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -785,7 +796,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="18.5">
+    <row r="3" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -837,7 +848,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="18.5">
+    <row r="4" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -882,7 +893,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="18.5">
+    <row r="5" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -919,7 +930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="18.5">
+    <row r="6" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -956,7 +967,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="18.5">
+    <row r="7" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -993,7 +1004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="18.5">
+    <row r="8" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1030,7 +1041,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="18.5">
+    <row r="9" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H9" s="5"/>
       <c r="I9" s="9" t="s">
         <v>34</v>
@@ -1049,7 +1060,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="18.5">
+    <row r="10" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1086,7 +1097,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="18.5">
+    <row r="11" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1123,7 +1134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="18.5">
+    <row r="12" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1160,7 +1171,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="18.5">
+    <row r="13" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1197,7 +1208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="18.5">
+    <row r="14" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1234,7 +1245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="18.5">
+    <row r="15" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H15" s="5"/>
       <c r="I15" s="9">
         <v>1</v>
@@ -1250,7 +1261,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="18.5">
+    <row r="16" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H16" s="5"/>
       <c r="I16" s="9">
         <v>2</v>
@@ -1266,7 +1277,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="18.5">
+    <row r="17" spans="1:13" ht="19" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1303,7 +1314,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="18.5">
+    <row r="18" spans="1:13" ht="19" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>14</v>
       </c>
@@ -1340,7 +1351,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="18.5">
+    <row r="19" spans="1:13" ht="19" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>15</v>
       </c>
@@ -1377,7 +1388,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="18.5">
+    <row r="20" spans="1:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H20" s="5"/>
       <c r="I20" s="9" t="s">
         <v>42</v>
@@ -1393,7 +1404,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="18.5">
+    <row r="21" spans="1:13" ht="19" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>16</v>
       </c>
@@ -1430,7 +1441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="18.5">
+    <row r="22" spans="1:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H22" s="5"/>
       <c r="I22" s="9" t="s">
         <v>44</v>
@@ -1446,7 +1457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.5">
+    <row r="23" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>17</v>
       </c>
@@ -1741,9 +1752,28 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C05051-7992-4C51-8E5B-6C6AF6A8AF44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56C05051-7992-4C51-8E5B-6C6AF6A8AF44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B4AD283-438F-4B0D-8521-6547D30B8E45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B4AD283-438F-4B0D-8521-6547D30B8E45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>